--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1389,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,1006 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,20 +436,20 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1100,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq38，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1117,10 +1141,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>06:36</t>
@@ -1159,7 +1199,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,1236 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/17</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>1/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq38，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq59，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1227,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1449,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -1482,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1506,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1704,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1743,7 +1759,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1815,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1926,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2148,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2259,7 +2275,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2386,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2497,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2592,7 +2608,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2719,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2830,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2925,7 +2941,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3052,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,7 +3163,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3274,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3369,7 +3385,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3480,7 +3496,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3595,7 +3611,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3710,7 +3726,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3764,6 +3780,684 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1687,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -1720,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1744,17 +1748,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1764,13 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,32 +1917,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1942,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1966,33 +1978,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -2020,32 +2036,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2053,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2077,33 +2097,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -2131,32 +2155,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2164,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2188,33 +2216,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/25</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2274,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2275,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2299,33 +2335,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2425,7 +2465,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2464,32 +2504,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>168分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2497,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2521,33 +2565,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/25</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2647,7 +2695,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2719,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2908,32 +2956,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2941,7 +2993,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2965,17 +3017,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -2985,13 +3037,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3163,7 +3219,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3274,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3385,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3496,7 +3552,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3550,7 +3606,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3726,7 +3782,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3837,7 +3893,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3952,7 +4008,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4063,7 +4119,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4174,7 +4230,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4228,7 +4284,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4345,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4343,7 +4399,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>7/25</t>
         </is>
       </c>
     </row>
@@ -4351,22 +4407,22 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4399,12 +4455,12 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4418,7 +4474,7 @@
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4455,6 +4511,1029 @@
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>7/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>12/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>10/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>168.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>11/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC44"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,18 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1954,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2127,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>17/25</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2246,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>15/25</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2541,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2595,7 +2599,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>16/25</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2767,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2806,7 +2810,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2878,7 +2882,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2966,19 +2970,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2993,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3032,22 +3036,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -3075,32 +3079,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3108,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3132,17 +3140,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3152,13 +3160,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -3186,32 +3198,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3219,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3243,33 +3259,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -3297,32 +3317,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3330,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3354,33 +3378,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>9/25</t>
         </is>
       </c>
     </row>
@@ -3408,32 +3436,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3441,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3465,17 +3497,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3485,13 +3517,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -3519,32 +3555,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3552,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3576,17 +3616,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3596,17 +3636,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>3/25</t>
         </is>
       </c>
     </row>
@@ -3634,32 +3674,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3667,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3691,17 +3735,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3711,12 +3755,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3749,32 +3793,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3782,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3806,33 +3854,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/25</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3932,7 +3984,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -3947,7 +3999,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3975,12 +4027,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4008,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4016,10 +4068,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr"/>
-      <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4119,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4197,32 +4265,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4230,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4254,17 +4326,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4274,17 +4346,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4399,7 +4471,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4499,7 +4571,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4571,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4625,7 +4697,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>12/25</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4797,7 +4869,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4851,7 +4923,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/25</t>
+          <t>13/25</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4984,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4966,7 +5038,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>17/25</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5099,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5081,7 +5153,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>6/25</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5214,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5196,7 +5268,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/25</t>
+          <t>15/25</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5329,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5368,7 +5440,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5479,7 +5551,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5533,7 +5605,804 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/25</t>
+          <t>16/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>9/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>9/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>9/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>1/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,13 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,13 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,13 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/25</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/25</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2369,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2480,7 +2492,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2599,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2710,7 +2722,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2821,7 +2833,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2944,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3048,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3051,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3289,7 +3301,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3408,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3539,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3658,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/25</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3777,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3884,7 +3896,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3999,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4044,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -4060,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4138,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4154,32 +4166,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4187,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4211,17 +4227,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4231,13 +4247,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4322,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,7 +4376,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4384,32 +4404,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4417,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4441,37 +4465,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4499,32 +4523,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4532,7 +4560,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4556,17 +4584,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4576,13 +4604,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4610,32 +4642,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4643,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4667,17 +4703,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4687,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/25</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4725,32 +4761,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -4758,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4782,17 +4822,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4802,13 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4836,32 +4880,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -4869,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4893,37 +4941,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/25</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4951,32 +4999,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -4984,7 +5036,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5008,17 +5060,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5028,17 +5080,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/25</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5151,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5153,7 +5205,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/25</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5181,32 +5233,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5214,7 +5270,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5238,17 +5294,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5258,17 +5314,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>15/25</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5385,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5379,7 +5435,7 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5496,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5490,7 +5546,7 @@
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5607,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5605,7 +5661,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/25</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5722,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5705,7 +5761,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5720,7 +5776,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5781,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5835,7 +5891,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5946,7 +6002,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6063,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6061,7 +6117,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/25</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6122,7 +6178,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6176,7 +6232,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/25</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6293,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6281,13 +6337,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6348,7 +6408,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6402,7 +6462,685 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>142.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,13 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,13 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,18 +2830,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3053,17 +3065,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3167,14 +3179,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3182,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,17 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3405,22 +3417,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,7 +3893,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3896,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4011,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4495,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4733,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5118,32 +5130,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5151,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,17 +5191,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5195,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5259,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
@@ -5270,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5309,22 +5325,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5352,32 +5368,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5385,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5409,17 +5429,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5429,13 +5449,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5463,32 +5487,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5496,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5520,17 +5548,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5540,13 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5574,32 +5606,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5607,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5631,17 +5667,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5651,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>168.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5689,32 +5725,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5722,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5746,17 +5786,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5766,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5804,32 +5844,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5837,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5861,37 +5905,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -5919,32 +5963,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5952,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5976,33 +6024,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6102,7 +6154,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6117,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -6145,32 +6197,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6178,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6202,17 +6258,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6222,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6293,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6347,7 +6403,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6462,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6523,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,7 +6690,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6799,7 +6855,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6916,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6971,7 +7027,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7025,7 +7081,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -7033,22 +7089,22 @@
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7081,12 +7137,12 @@
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7100,47 +7156,622 @@
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr">
         <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
           <t>13:42</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W57" s="2" t="inlineStr">
+      <c r="W58" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X57" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y57" s="2" t="inlineStr">
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z57" s="2" t="inlineStr">
+      <c r="Z58" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>147.0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>15/28</t>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,17 +1066,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4013,17 +4013,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -5973,24 +5973,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6082,32 +6082,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6139,17 +6143,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6159,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6207,24 +6211,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6234,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6283,12 +6287,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6316,32 +6320,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -6349,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,32 +6381,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6431,32 +6439,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6464,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,17 +6500,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6508,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6546,12 +6558,12 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6579,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6587,10 +6599,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="inlineStr"/>
-      <c r="R52" s="2" t="inlineStr"/>
-      <c r="S52" s="2" t="inlineStr"/>
-      <c r="T52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -6690,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6729,7 +6757,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6801,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6855,7 +6883,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7027,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7081,7 +7109,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -7142,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7257,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7372,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7421,12 +7449,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7515,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7531,17 +7559,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7630,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7656,7 +7684,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7717,7 +7745,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7775,6 +7803,462 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6449,24 +6449,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq44，推进6站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,14 +2128,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>149.0</t>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,17 +3065,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,14 +3536,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>146.0</t>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       <c r="AB31" s="2" t="inlineStr"/>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,14 +5087,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>149.0</t>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6330,24 +6330,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6461,12 +6461,12 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq47，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       <c r="AB52" s="2" t="inlineStr"/>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6685,32 +6685,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -6718,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,17 +6746,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6762,13 +6766,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6796,32 +6804,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6829,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6853,17 +6865,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6873,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>139.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6911,32 +6923,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6944,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6968,17 +6984,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6988,13 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB55" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7042,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7055,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7079,17 +7103,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7099,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7137,32 +7161,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7170,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7194,17 +7222,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7214,17 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7252,32 +7280,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7285,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7309,17 +7341,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7329,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7454,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7569,7 +7601,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7716,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7799,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7909,12 +7941,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7975,7 +8007,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8029,7 +8061,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8134,13 +8166,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -8201,7 +8237,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8255,7 +8291,689 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2835,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,14 +3774,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,14 +6999,14 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7183,12 +7183,12 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7290,19 +7290,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7399,32 +7399,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7432,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7456,17 +7460,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7476,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7744,32 +7748,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7777,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7801,17 +7809,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7821,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7859,32 +7867,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7892,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7916,17 +7928,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7936,17 +7948,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7974,32 +7986,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8007,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8031,17 +8047,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8051,17 +8067,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8237,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8291,7 +8307,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8463,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8578,7 +8594,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8632,7 +8648,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8709,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8747,7 +8763,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8824,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8923,7 +8939,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8977,6 +8993,811 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>139.3</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC79"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,14 +3060,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,17 +4854,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,14 +4968,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,14 +5206,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,14 +5801,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,22 +6761,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,14 +7118,14 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
           <t>138.0</t>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,14 +7356,14 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>135.7</t>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7877,24 +7877,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7953,12 +7953,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7996,24 +7996,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8062,17 +8062,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>137.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8105,32 +8105,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -8138,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,37 +8166,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8307,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8446,12 +8450,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq40，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -8479,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8487,10 +8491,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="inlineStr"/>
-      <c r="R68" s="2" t="inlineStr"/>
-      <c r="S68" s="2" t="inlineStr"/>
-      <c r="T68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>物理seq30（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq30映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8561,32 +8581,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -8594,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8618,17 +8642,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8638,17 +8662,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8824,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8939,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9050,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9104,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9165,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9219,7 +9243,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9334,7 +9358,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9419,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9510,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9564,7 +9588,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -9625,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9679,7 +9703,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9764,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9794,7 +9818,697 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>137.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:07</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4254,22 +4254,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8224,32 +8224,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8257,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8281,37 +8285,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8411,7 +8415,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8455,7 +8459,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq40，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程46%处后消失；随后反向物理轨迹由seq29推进至seq63，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -8483,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8591,24 +8595,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8618,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8667,12 +8671,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8772,7 +8776,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8815,32 +8819,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -8848,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,17 +8880,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8892,12 +8900,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9074,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9113,7 +9121,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9189,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9228,7 +9236,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9304,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9419,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9473,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9649,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9764,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9879,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9933,7 +9941,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10048,7 +10056,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10117,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10163,7 +10171,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10232,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10339,7 +10347,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10393,7 +10401,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10462,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10512,6 +10520,692 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1307,22 +1307,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,14 +2128,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,22 +3774,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,14 +5087,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8895,14 +8895,14 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
           <t>147.0</t>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9049,32 +9049,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9082,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,17 +9110,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9126,17 +9130,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9236,7 +9240,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9251,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9283,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9312,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9336,37 +9344,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9394,32 +9402,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9427,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,37 +9463,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>147.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9554,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9624,32 +9636,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -9657,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,17 +9697,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9701,17 +9717,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9826,7 +9842,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9903,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9941,7 +9957,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10056,7 +10072,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10171,7 +10187,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10286,7 +10302,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10347,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10401,7 +10417,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10516,7 +10532,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10593,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10631,7 +10647,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10708,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10803,7 +10819,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10857,7 +10873,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10934,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10972,7 +10988,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -11033,7 +11049,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11072,7 +11088,7 @@
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11087,7 +11103,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11095,22 +11111,22 @@
       <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11143,12 +11159,12 @@
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11162,47 +11178,737 @@
       <c r="T91" s="2" t="inlineStr"/>
       <c r="U91" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W91" s="2" t="inlineStr">
+      <c r="W92" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X91" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y91" s="2" t="inlineStr">
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z91" s="2" t="inlineStr">
+      <c r="Z92" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB91" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
-      <c r="AC91" s="2" t="inlineStr">
-        <is>
-          <t>3/29</t>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:59</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>147.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC97"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3184,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,17 +4497,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4730,22 +4730,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9646,24 +9646,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9712,22 +9712,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9755,32 +9755,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9788,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9812,17 +9816,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9832,17 +9836,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>139.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9870,32 +9874,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9903,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9927,17 +9935,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9947,17 +9955,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10133,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10363,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10478,7 +10486,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10593,7 +10601,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10647,7 +10655,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10716,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10819,7 +10827,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10873,7 +10881,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10934,7 +10942,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11049,7 +11057,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11103,7 +11111,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11164,7 +11172,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11279,7 +11287,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11333,7 +11341,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11394,7 +11402,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11448,7 +11456,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11517,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11563,7 +11571,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11624,7 +11632,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11739,7 +11747,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11854,7 +11862,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11912,6 +11920,121 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:31</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC98"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3065,12 +3065,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7123,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,12 +7361,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,17 +8067,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9777,12 +9777,12 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9884,24 +9884,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9993,32 +9993,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10026,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10050,37 +10054,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10108,32 +10112,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10141,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10165,17 +10173,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10185,17 +10193,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10338,32 +10346,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10371,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10395,17 +10407,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10415,17 +10427,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>137.3</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10453,32 +10465,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10486,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10510,17 +10526,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10530,12 +10546,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10601,7 +10617,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10655,7 +10671,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10827,7 +10843,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10942,7 +10958,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11057,7 +11073,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11111,7 +11127,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11172,7 +11188,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11226,7 +11242,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11287,7 +11303,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11341,7 +11357,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11418,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11456,7 +11472,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11517,7 +11533,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11571,7 +11587,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11648,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11747,7 +11763,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11862,7 +11878,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11916,7 +11932,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11993,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12031,7 +12047,122 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2950,13 +2950,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3070,12 +3074,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3313,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3432,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3541,17 +3545,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3665,12 +3669,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3789,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4259,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4388,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,12 +4858,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4983,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5102,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5225,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5334,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5701,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,12 +5815,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5935,7 +5939,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6058,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6292,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6415,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6776,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,17 +7246,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7370,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7494,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7720,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7958,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8072,12 +8076,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8305,17 +8309,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8376,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8420,13 +8424,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8666,12 +8674,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8737,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,17 +8789,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8910,7 +8918,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9086,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9140,7 +9148,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9201,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9255,7 +9263,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9374,7 +9382,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9493,7 +9501,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9846,7 +9854,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10084,7 +10092,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10203,7 +10211,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10326,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10356,24 +10364,24 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -10383,7 +10391,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10432,12 +10440,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>141.8</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10475,24 +10483,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10502,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10551,12 +10559,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10584,32 +10592,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10617,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10641,17 +10653,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10661,17 +10673,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>146.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -10699,32 +10711,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10732,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10756,17 +10772,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10776,13 +10792,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB87" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10830,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10843,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10867,17 +10891,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10887,17 +10911,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10925,32 +10949,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10958,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10982,17 +11010,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11002,17 +11030,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11073,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11127,7 +11155,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11155,32 +11183,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -11188,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11212,17 +11244,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11232,12 +11264,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11303,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11357,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11417,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq51，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -11418,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11426,10 +11458,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q93" s="2" t="inlineStr"/>
-      <c r="R93" s="2" t="inlineStr"/>
-      <c r="S93" s="2" t="inlineStr"/>
-      <c r="T93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>20:34</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -11472,7 +11520,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11533,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11587,7 +11635,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11648,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11702,7 +11750,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11817,7 +11865,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11932,7 +11980,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11993,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12108,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12162,7 +12210,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-浦东35路.xlsx
+++ b/data/export/2026-09-24-浦东35路.xlsx
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1312,17 +1312,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5929,17 +5929,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7714,17 +7714,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8908,17 +8908,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9263,7 +9263,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,17 +9372,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9735,7 +9735,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11040,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11101,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq51，推进23站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11548,32 +11548,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11581,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11605,17 +11609,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11625,17 +11629,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -11663,32 +11667,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11696,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11720,17 +11728,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11740,17 +11748,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -11778,32 +11786,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11811,7 +11823,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11835,17 +11847,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11855,17 +11867,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>147.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11893,32 +11905,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11926,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11950,17 +11966,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11970,17 +11986,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12041,7 +12057,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12095,7 +12111,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12172,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
